--- a/enrollment/004_swimming_competition_enrollment--enrollment.xlsx
+++ b/enrollment/004_swimming_competition_enrollment--enrollment.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'freestyle',_'label':_'freestyle'}</t>
+          <t>freestyle</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'freestyle', 'label': 'Freestyle'}</t>
+          <t>Freestyle</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'breaststroke',_'label':_'breaststroke'}</t>
+          <t>breaststroke</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'breaststroke', 'label': 'Breaststroke'}</t>
+          <t>Breaststroke</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'backstroke',_'label':_'backstroke'}</t>
+          <t>backstroke</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'backstroke', 'label': 'Backstroke'}</t>
+          <t>Backstroke</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'local',_'label':_'local'}</t>
+          <t>local</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'local', 'label': 'Local'}</t>
+          <t>Local</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'regional',_'label':_'regional'}</t>
+          <t>regional</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'regional', 'label': 'Regional'}</t>
+          <t>Regional</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'national',_'label':_'national'}</t>
+          <t>national</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'national', 'label': 'National'}</t>
+          <t>National</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'8-12',_'label':_'8-12'}</t>
+          <t>8-12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': '8-12', 'label': '8-12'}</t>
+          <t>8-12</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'13-15',_'label':_'13-15'}</t>
+          <t>13-15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': '13-15', 'label': '13-15'}</t>
+          <t>13-15</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'16-20',_'label':_'16-20'}</t>
+          <t>16-20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': '16-20', 'label': '16-20'}</t>
+          <t>16-20</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'male',_'label':_'male'}</t>
+          <t>male</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'male', 'label': 'Male'}</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'female',_'label':_'female'}</t>
+          <t>female</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'female', 'label': 'Female'}</t>
+          <t>Female</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
